--- a/untranslated/downloads/data-excel/11.6.1.1.xlsx
+++ b/untranslated/downloads/data-excel/11.6.1.1.xlsx
@@ -1,15 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E4692AF-B7E0-4A8E-BB5C-BA37770B33A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -64,7 +76,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -166,11 +178,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -181,10 +190,13 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -205,9 +217,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -245,9 +257,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -282,7 +294,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -317,7 +329,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -490,14 +502,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:R6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="37" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -519,7 +531,7 @@
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
     </row>
-    <row r="2" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -537,8 +549,9 @@
       <c r="O2" s="3"/>
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -590,8 +603,11 @@
       <c r="Q3" s="8">
         <v>2023</v>
       </c>
+      <c r="R3" s="8">
+        <v>2024</v>
+      </c>
     </row>
-    <row r="4" spans="1:17" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>6</v>
       </c>
@@ -601,156 +617,165 @@
       <c r="C4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="12">
         <v>214.64335233400089</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="12">
         <v>223.17286485664306</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="12">
         <v>183.17358892438764</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="12">
         <v>215.12617344044503</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="12">
         <v>178.26040210730025</v>
       </c>
-      <c r="I4" s="13">
+      <c r="I4" s="12">
         <v>195.24385752617454</v>
       </c>
-      <c r="J4" s="13">
+      <c r="J4" s="12">
         <v>170.94442632238571</v>
       </c>
-      <c r="K4" s="13">
+      <c r="K4" s="12">
         <v>165.14394360035669</v>
       </c>
-      <c r="L4" s="13">
+      <c r="L4" s="12">
         <v>172.67633487145682</v>
       </c>
-      <c r="M4" s="14">
+      <c r="M4" s="13">
         <v>185.05797171560801</v>
       </c>
-      <c r="N4" s="14">
+      <c r="N4" s="13">
         <f>N5/N6*1000</f>
         <v>185.91274954506002</v>
       </c>
-      <c r="O4" s="14">
+      <c r="O4" s="13">
         <f>O5/O6*1000</f>
         <v>191.02362938681662</v>
       </c>
-      <c r="P4" s="14">
+      <c r="P4" s="13">
         <f>P5/P6*1000</f>
         <v>212.61804618681055</v>
       </c>
-      <c r="Q4" s="14">
+      <c r="Q4" s="13">
         <v>279.01945525291825</v>
       </c>
+      <c r="R4" s="15">
+        <v>251.5</v>
+      </c>
     </row>
-    <row r="5" spans="1:17" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="13">
         <v>1114.5999999999999</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="13">
         <v>1173.8</v>
       </c>
-      <c r="F5" s="15">
+      <c r="F5" s="13">
         <v>980.4</v>
       </c>
-      <c r="G5" s="15">
+      <c r="G5" s="13">
         <v>1175.5999999999999</v>
       </c>
-      <c r="H5" s="15">
+      <c r="H5" s="13">
         <v>994.9</v>
       </c>
-      <c r="I5" s="15">
+      <c r="I5" s="13">
         <v>1113.3</v>
       </c>
-      <c r="J5" s="15">
+      <c r="J5" s="13">
         <v>995.7</v>
       </c>
-      <c r="K5" s="15">
+      <c r="K5" s="13">
         <v>981.5</v>
       </c>
-      <c r="L5" s="15">
+      <c r="L5" s="13">
         <v>1047.8</v>
       </c>
-      <c r="M5" s="15">
+      <c r="M5" s="13">
         <v>1147.5999999999999</v>
       </c>
-      <c r="N5" s="15">
+      <c r="N5" s="13">
         <v>1175.9000000000001</v>
       </c>
-      <c r="O5" s="15">
+      <c r="O5" s="13">
         <v>1229.5999999999999</v>
       </c>
-      <c r="P5" s="15">
+      <c r="P5" s="13">
         <v>1339.6</v>
       </c>
-      <c r="Q5" s="15">
+      <c r="Q5" s="13">
         <v>1792.7</v>
       </c>
+      <c r="R5" s="2">
+        <v>1646.5</v>
+      </c>
     </row>
-    <row r="6" spans="1:17" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="12" t="s">
+    <row r="6" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="14">
         <v>5192.8</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="14">
         <v>5259.6</v>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="14">
         <v>5352.3</v>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="14">
         <v>5464.7</v>
       </c>
-      <c r="H6" s="16">
+      <c r="H6" s="14">
         <v>5580.6</v>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="14">
         <v>5702.1</v>
       </c>
-      <c r="J6" s="16">
+      <c r="J6" s="14">
         <v>5824.7</v>
       </c>
-      <c r="K6" s="16">
+      <c r="K6" s="14">
         <v>5943.3</v>
       </c>
-      <c r="L6" s="16">
+      <c r="L6" s="14">
         <v>6068</v>
       </c>
-      <c r="M6" s="16">
+      <c r="M6" s="14">
         <v>6201.3</v>
       </c>
-      <c r="N6" s="16">
+      <c r="N6" s="14">
         <v>6325.01</v>
       </c>
-      <c r="O6" s="16">
+      <c r="O6" s="14">
         <v>6436.9</v>
       </c>
-      <c r="P6" s="16">
+      <c r="P6" s="14">
         <v>6300.5</v>
       </c>
-      <c r="Q6" s="16">
+      <c r="Q6" s="14">
         <v>6425</v>
+      </c>
+      <c r="R6" s="16">
+        <v>6547.1</v>
       </c>
     </row>
   </sheetData>
